--- a/SuppXLS/Scen_Z_TIMESReport.xlsx
+++ b/SuppXLS/Scen_Z_TIMESReport.xlsx
@@ -392,7 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249880000948906"/>
+        <fgColor theme="0" tint="-0.249870002269745"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249970003962517"/>
+        <fgColor theme="0" tint="-0.249960005283356"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/SuppXLS/Scen_Z_TIMESReport.xlsx
+++ b/SuppXLS/Scen_Z_TIMESReport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kristoffer\DemoS_012_timesreport\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F378AE75-CC66-44B8-909D-E7481FF6BDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4950" yWindow="3480" windowWidth="26775" windowHeight="12000" activeTab="3"/>
+    <workbookView xWindow="-34670" yWindow="-110" windowWidth="34780" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UserInput" sheetId="18" r:id="rId3"/>
-    <sheet name="WriteSets2GDXfile" sheetId="15" r:id="rId4"/>
-    <sheet name="TIMESreport_Switches" sheetId="19" r:id="rId5"/>
-    <sheet name="RunTIMESReportScript" sheetId="11" r:id="rId6"/>
+    <sheet name="UserInput" sheetId="18" r:id="rId1"/>
+    <sheet name="WriteSets2GDXfile" sheetId="15" r:id="rId2"/>
+    <sheet name="TIMESreport_Switches" sheetId="19" r:id="rId3"/>
+    <sheet name="RunTIMESReportScript" sheetId="11" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="filename" localSheetId="2">RunTIMESReportScript!$C$12</definedName>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="193">
   <si>
     <t>Attribute</t>
   </si>
@@ -163,9 +164,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Keep information on FLO_TAX as part of GDX output</t>
-  </si>
-  <si>
     <t>FLO~1</t>
   </si>
   <si>
@@ -650,6 +648,18 @@
   </si>
   <si>
     <t>Copy user defined sets commodity sets related to timesreport.gms from [Sets-DemoModels.xlsx]TIMESreport_Sets-Comm'!A2:C. That is user defined processes sets related to comgroup.</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>$SET ANNCOST LEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep information on FLO_TAX etc. as part of GDX output </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNCOST LEV option to ensure that costs are NOT accounted for in years before model horizont (BOH) </t>
   </si>
 </sst>
 </file>
@@ -660,7 +670,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -723,7 +733,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -763,6 +773,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -785,13 +802,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249540001153946"/>
+        <fgColor indexed="43"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="43"/>
+        <fgColor theme="0" tint="-0.24939725943784904"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,7 +820,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249630004167557"/>
+        <fgColor theme="0" tint="-0.24948881496627703"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,6 +846,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -841,6 +859,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -851,6 +870,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -861,68 +881,31 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="53">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="1">
       <alignment horizontal="right" vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="1">
       <alignment horizontal="right" vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" applyBorder="0">
       <alignment horizontal="right" vertical="center"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -930,77 +913,26 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1013,7 +945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1032,180 +964,85 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="26" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="26" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="37" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="18" quotePrefix="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="18"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="37"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="28" applyFill="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="28" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="39" applyFill="1">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="26" applyFill="1">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="9" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="20" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="7" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="37" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="18" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="43">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="44">
-      <alignment/>
-      <protection/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="24"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="25"/>
   </cellXfs>
-  <cellStyles count="39">
+  <cellStyles count="34">
+    <cellStyle name="5x indented GHG Textfiels" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="AggOrange_CRFReport-template" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="AggOrange9_CRFReport-template" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="CustomizationCells" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Euro" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Hyperlink" xfId="18" builtinId="8"/>
+    <cellStyle name="InputCells" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Migliaia_tab emissioni" xfId="22" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
-    <cellStyle name="5x indented GHG Textfiels" xfId="20"/>
-    <cellStyle name="AggOrange_CRFReport-template" xfId="21"/>
-    <cellStyle name="AggOrange9_CRFReport-template" xfId="22"/>
-    <cellStyle name="CustomizationCells" xfId="23"/>
-    <cellStyle name="Euro" xfId="24"/>
-    <cellStyle name="InputCells" xfId="25"/>
-    <cellStyle name="Normal 10" xfId="26"/>
-    <cellStyle name="Normal 2" xfId="27"/>
-    <cellStyle name="Normal 3" xfId="28"/>
-    <cellStyle name="Normal 4" xfId="29"/>
-    <cellStyle name="Normal GHG Numbers (0.00)" xfId="30"/>
-    <cellStyle name="Normal GHG Textfiels Bold" xfId="31"/>
-    <cellStyle name="Normal GHG-Shade" xfId="32"/>
-    <cellStyle name="Normale_B2020" xfId="33"/>
-    <cellStyle name="Percent 2" xfId="34"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="35"/>
-    <cellStyle name="Обычный_CRF2002 (1)" xfId="36"/>
-    <cellStyle name="Hyperlink" xfId="37" builtinId="8"/>
-    <cellStyle name="Normal 5" xfId="38"/>
-    <cellStyle name="Normal 10 2" xfId="39"/>
-    <cellStyle name="Normal 6" xfId="40"/>
-    <cellStyle name="Migliaia_tab emissioni" xfId="41"/>
-    <cellStyle name="Normal 7" xfId="42"/>
-    <cellStyle name="Normal 9" xfId="43"/>
-    <cellStyle name="Normal 12" xfId="44"/>
-    <cellStyle name="Normal 8" xfId="45"/>
-    <cellStyle name="Normal 5 2" xfId="46"/>
-    <cellStyle name="Normal 3 2" xfId="47"/>
-    <cellStyle name="Normal 11" xfId="48"/>
-    <cellStyle name="Normal 5 3" xfId="49"/>
-    <cellStyle name="Normal 3 3" xfId="50"/>
-    <cellStyle name="Normal 12 2" xfId="51"/>
-    <cellStyle name="Normal 12 3" xfId="52"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 10 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Normal 11" xfId="29" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Normal 12" xfId="25" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Normal 12 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 12 3" xfId="33" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 3" xfId="9" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 3 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Normal 3 3" xfId="31" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 4" xfId="10" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 5" xfId="19" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Normal 5 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Normal 5 3" xfId="30" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 6" xfId="21" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Normal 7" xfId="23" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Normal 8" xfId="26" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Normal 9" xfId="24" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Normal GHG Numbers (0.00)" xfId="11" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normal GHG Textfiels Bold" xfId="12" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal GHG-Shade" xfId="13" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Normale_B2020" xfId="14" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Percent 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="16" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Обычный_CRF2002 (1)" xfId="17" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1218,26 +1055,26 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>606137</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>291398</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>103910</xdr:rowOff>
+      <xdr:rowOff>95627</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>165610</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>463784</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>17319</xdr:rowOff>
+      <xdr:rowOff>9036</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{d9c76a1a-5743-9853-b8f7-1f910af6fc01}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C76A1A-5743-9853-B8F7-1F910AF6FC01}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1246,17 +1083,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11658600" y="104775"/>
-          <a:ext cx="4438650" cy="5705475"/>
+          <a:off x="13782675" y="95250"/>
+          <a:ext cx="4438650" cy="6010275"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1550,27 +1389,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBE96D8-A835-430C-ADC5-007534119BFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBE96D8-A835-430C-ADC5-007534119BFE}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K196"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="22.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="16"/>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:8" ht="56.25" customHeight="1">
+    <row r="2" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1578,12 +1417,12 @@
         <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="71.25" customHeight="1">
+    <row r="3" spans="1:11" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>12</v>
       </c>
@@ -1602,11 +1441,11 @@
       <c r="H3" s="5"/>
       <c r="K3" s="19"/>
     </row>
-    <row r="4" spans="1:5" ht="14.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="E4" s="16"/>
     </row>
-    <row r="5" spans="1:11" ht="14.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="B5" s="20" t="s">
         <v>20</v>
@@ -1629,1352 +1468,1352 @@
       </c>
       <c r="K5" s="18"/>
     </row>
-    <row r="6" spans="1:8" ht="14.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" t="s">
         <v>97</v>
       </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
         <v>64</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>65</v>
       </c>
-      <c r="H6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.5">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
         <v>67</v>
       </c>
-      <c r="G7" t="s">
-        <v>68</v>
-      </c>
       <c r="H7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
         <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
         <v>69</v>
       </c>
-      <c r="G8" t="s">
-        <v>70</v>
-      </c>
       <c r="H8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
         <v>94</v>
       </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="s">
         <v>71</v>
       </c>
-      <c r="G9" t="s">
-        <v>72</v>
-      </c>
       <c r="H9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
       <c r="H10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
         <v>75</v>
       </c>
-      <c r="G11" t="s">
-        <v>76</v>
-      </c>
       <c r="H11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
         <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="G13" s="40" t="s">
-        <v>179</v>
-      </c>
       <c r="H13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G14" t="s">
         <v>180</v>
       </c>
-      <c r="G14" t="s">
-        <v>181</v>
-      </c>
       <c r="H14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="14.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="38"/>
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
     </row>
-    <row r="16" spans="1:8" ht="14.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="38"/>
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
     </row>
-    <row r="17" spans="1:8" ht="14.5">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="38"/>
       <c r="G17" s="38"/>
       <c r="H17" s="38"/>
     </row>
-    <row r="18" spans="1:8" ht="14.5">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="38"/>
       <c r="G18" s="38"/>
       <c r="H18" s="38"/>
     </row>
-    <row r="19" spans="1:8" ht="14.5">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="38"/>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
     </row>
-    <row r="20" spans="1:8" ht="14.5">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="39"/>
       <c r="G20" s="39"/>
       <c r="H20" s="39"/>
     </row>
-    <row r="21" spans="1:5" ht="14.5">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" s="16"/>
     </row>
-    <row r="22" spans="1:5" ht="14.5">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="16"/>
     </row>
-    <row r="23" spans="1:5" ht="14.5">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" s="16"/>
     </row>
-    <row r="24" spans="1:5" ht="14.5">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" s="16"/>
     </row>
-    <row r="25" spans="1:5" ht="14.5">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25" s="16"/>
     </row>
-    <row r="26" spans="1:5" ht="14.5">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26" s="16"/>
     </row>
-    <row r="27" spans="1:5" ht="14.5">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" s="16"/>
     </row>
-    <row r="28" spans="1:5" ht="14.5">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
         <v>132</v>
       </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E28" s="16"/>
     </row>
-    <row r="29" spans="1:5" ht="14.5">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" t="s">
         <v>122</v>
       </c>
-      <c r="C29" t="s">
-        <v>123</v>
-      </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="16"/>
     </row>
-    <row r="30" spans="1:5" ht="14.5">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
         <v>101</v>
       </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E30" s="16"/>
     </row>
-    <row r="31" spans="1:5" ht="14.5">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s">
         <v>116</v>
       </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31" s="16"/>
     </row>
-    <row r="32" spans="1:5" ht="14.5">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" t="s">
         <v>134</v>
       </c>
-      <c r="C32" t="s">
-        <v>135</v>
-      </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" s="16"/>
     </row>
-    <row r="33" spans="1:5" ht="14.5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" t="s">
         <v>128</v>
       </c>
-      <c r="C33" t="s">
-        <v>129</v>
-      </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E33" s="16"/>
     </row>
-    <row r="34" spans="1:5" ht="14.5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
         <v>99</v>
       </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E34" s="16"/>
     </row>
-    <row r="35" spans="1:5" ht="14.5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s">
         <v>118</v>
       </c>
-      <c r="C35" t="s">
-        <v>119</v>
-      </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35" s="16"/>
     </row>
-    <row r="36" spans="1:5" ht="14.5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" t="s">
         <v>103</v>
       </c>
-      <c r="C36" t="s">
-        <v>104</v>
-      </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E36" s="16"/>
     </row>
-    <row r="37" spans="1:5" ht="14.5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
         <v>105</v>
       </c>
-      <c r="C37" t="s">
-        <v>106</v>
-      </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37" s="16"/>
     </row>
-    <row r="38" spans="1:5" ht="14.5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" t="s">
         <v>183</v>
       </c>
-      <c r="C38" t="s">
-        <v>184</v>
-      </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38" s="16"/>
     </row>
-    <row r="39" spans="1:5" ht="14.5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
         <v>126</v>
       </c>
-      <c r="C39" t="s">
-        <v>127</v>
-      </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="40" spans="1:5" ht="14.5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s">
         <v>114</v>
       </c>
-      <c r="C40" t="s">
-        <v>115</v>
-      </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E40" s="16"/>
     </row>
-    <row r="41" spans="1:5" ht="14.5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" t="s">
         <v>109</v>
       </c>
-      <c r="C41" t="s">
-        <v>110</v>
-      </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41" s="16"/>
     </row>
-    <row r="42" spans="1:5" ht="14.5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
         <v>124</v>
       </c>
-      <c r="C42" t="s">
-        <v>125</v>
-      </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:5" ht="14.5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" t="s">
-        <v>131</v>
-      </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:5" ht="14.5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
         <v>139</v>
       </c>
-      <c r="C44" t="s">
-        <v>140</v>
-      </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E44" s="16"/>
     </row>
-    <row r="45" spans="1:5" ht="14.5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" t="s">
         <v>120</v>
       </c>
-      <c r="C45" t="s">
-        <v>121</v>
-      </c>
       <c r="D45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:5" ht="14.5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" t="s">
         <v>111</v>
       </c>
-      <c r="C46" t="s">
-        <v>112</v>
-      </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E46" s="16"/>
     </row>
-    <row r="47" spans="1:5" ht="14.5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" t="s">
         <v>107</v>
       </c>
-      <c r="C47" t="s">
-        <v>108</v>
-      </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="1:5" ht="14.5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" t="s">
         <v>141</v>
       </c>
-      <c r="C48" t="s">
-        <v>142</v>
-      </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="16"/>
     </row>
-    <row r="49" spans="1:5" ht="14.5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
       <c r="B49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" t="s">
         <v>148</v>
       </c>
-      <c r="C49" t="s">
-        <v>149</v>
-      </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="16"/>
     </row>
-    <row r="50" spans="1:5" ht="14.5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s">
         <v>146</v>
       </c>
-      <c r="C50" t="s">
-        <v>147</v>
-      </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E50" s="16"/>
     </row>
-    <row r="51" spans="1:5" ht="14.5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" t="s">
         <v>143</v>
       </c>
-      <c r="C51" t="s">
-        <v>144</v>
-      </c>
       <c r="D51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E51" s="16"/>
     </row>
-    <row r="52" spans="1:5" ht="14.5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" t="s">
         <v>151</v>
       </c>
-      <c r="C52" t="s">
-        <v>152</v>
-      </c>
       <c r="D52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E52" s="16"/>
     </row>
-    <row r="53" spans="1:5" ht="14.5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E53" s="16"/>
     </row>
-    <row r="54" spans="1:5" ht="14.5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E54" s="16"/>
     </row>
-    <row r="55" spans="1:5" ht="14.5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E55" s="16"/>
     </row>
-    <row r="56" spans="1:5" ht="14.5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E56" s="16"/>
     </row>
-    <row r="57" spans="1:5" ht="14.5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E57" s="16"/>
     </row>
-    <row r="58" spans="1:5" ht="14.5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" t="s">
         <v>176</v>
       </c>
-      <c r="C58" t="s">
-        <v>177</v>
-      </c>
       <c r="D58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58" s="16"/>
     </row>
-    <row r="59" spans="1:5" ht="14.5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" t="s">
+        <v>184</v>
+      </c>
+      <c r="C59" t="s">
         <v>185</v>
       </c>
-      <c r="C59" t="s">
-        <v>186</v>
-      </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E59" s="16"/>
     </row>
-    <row r="60" spans="1:5" ht="14.5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="E60" s="16"/>
     </row>
-    <row r="61" spans="1:5" ht="14.5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
       <c r="E61" s="16"/>
     </row>
-    <row r="62" spans="1:5" ht="14.5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="16"/>
       <c r="E62" s="16"/>
     </row>
-    <row r="63" spans="1:5" ht="14.5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="16"/>
       <c r="E63" s="16"/>
     </row>
-    <row r="64" spans="1:5" ht="14.5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
       <c r="E64" s="16"/>
     </row>
-    <row r="65" spans="1:5" ht="14.5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="16"/>
       <c r="E65" s="16"/>
     </row>
-    <row r="66" spans="1:5" ht="14.5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
       <c r="E66" s="16"/>
     </row>
-    <row r="67" spans="1:5" ht="14.5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="16"/>
       <c r="E67" s="16"/>
     </row>
-    <row r="68" spans="1:5" ht="14.5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="16"/>
       <c r="E68" s="16"/>
     </row>
-    <row r="69" spans="1:5" ht="14.5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="16"/>
       <c r="E69" s="16"/>
     </row>
-    <row r="70" spans="1:5" ht="14.5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="16"/>
       <c r="E70" s="16"/>
     </row>
-    <row r="71" spans="1:5" ht="14.5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="16"/>
       <c r="E71" s="16"/>
     </row>
-    <row r="72" spans="1:5" ht="14.5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="E72" s="16"/>
     </row>
-    <row r="73" spans="1:5" ht="14.5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="16"/>
       <c r="E73" s="16"/>
     </row>
-    <row r="74" spans="1:5" ht="14.5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="16"/>
       <c r="E74" s="16"/>
     </row>
-    <row r="75" spans="1:5" ht="14.5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
       <c r="E75" s="16"/>
     </row>
-    <row r="76" spans="1:5" ht="14.5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="E76" s="16"/>
     </row>
-    <row r="77" spans="1:5" ht="14.5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="E77" s="16"/>
     </row>
-    <row r="78" spans="1:5" ht="14.5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="E78" s="16"/>
     </row>
-    <row r="79" spans="1:5" ht="14.5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="E79" s="16"/>
     </row>
-    <row r="80" spans="1:5" ht="14.5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="E80" s="16"/>
     </row>
-    <row r="81" spans="1:5" ht="14.5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="E81" s="16"/>
     </row>
-    <row r="82" spans="1:5" ht="14.5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="E82" s="16"/>
     </row>
-    <row r="83" spans="1:5" ht="14.5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="16"/>
       <c r="E83" s="16"/>
     </row>
-    <row r="84" spans="1:5" ht="14.5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="16"/>
       <c r="E84" s="16"/>
     </row>
-    <row r="85" spans="1:5" ht="14.5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="16"/>
       <c r="E85" s="16"/>
     </row>
-    <row r="86" spans="1:5" ht="14.5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="16"/>
       <c r="E86" s="16"/>
     </row>
-    <row r="87" spans="1:5" ht="14.5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="E87" s="16"/>
     </row>
-    <row r="88" spans="1:5" ht="14.5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="E88" s="16"/>
     </row>
-    <row r="89" spans="1:5" ht="14.5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="E89" s="16"/>
     </row>
-    <row r="90" spans="1:5" ht="14.5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="E90" s="16"/>
     </row>
-    <row r="91" spans="1:5" ht="14.5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="E91" s="16"/>
     </row>
-    <row r="92" spans="1:5" ht="14.5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="E92" s="16"/>
     </row>
-    <row r="93" spans="1:5" ht="14.5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="16"/>
       <c r="E93" s="16"/>
     </row>
-    <row r="94" spans="1:5" ht="14.5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="E94" s="16"/>
     </row>
-    <row r="95" spans="1:5" ht="14.5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="E95" s="16"/>
     </row>
-    <row r="96" spans="1:5" ht="14.5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="E96" s="16"/>
     </row>
-    <row r="97" spans="1:5" ht="14.5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="E97" s="16"/>
     </row>
-    <row r="98" spans="1:5" ht="14.5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="16"/>
       <c r="E98" s="16"/>
     </row>
-    <row r="99" spans="1:5" ht="14.5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="16"/>
       <c r="E99" s="16"/>
     </row>
-    <row r="100" spans="1:5" ht="14.5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="E100" s="16"/>
     </row>
-    <row r="101" spans="1:5" ht="14.5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="16"/>
       <c r="E101" s="16"/>
     </row>
-    <row r="102" spans="1:5" ht="14.5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="16"/>
       <c r="E102" s="16"/>
     </row>
-    <row r="103" spans="1:5" ht="14.5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="16"/>
       <c r="E103" s="16"/>
     </row>
-    <row r="104" spans="1:5" ht="14.5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="E104" s="16"/>
     </row>
-    <row r="105" spans="1:5" ht="14.5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="16"/>
       <c r="E105" s="16"/>
     </row>
-    <row r="106" spans="1:5" ht="14.5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="16"/>
       <c r="E106" s="16"/>
     </row>
-    <row r="107" spans="1:5" ht="14.5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="16"/>
       <c r="E107" s="16"/>
     </row>
-    <row r="108" spans="1:5" ht="14.5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="E108" s="16"/>
     </row>
-    <row r="109" spans="1:5" ht="14.5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="16"/>
       <c r="E109" s="16"/>
     </row>
-    <row r="110" spans="1:5" ht="14.5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="16"/>
       <c r="E110" s="16"/>
     </row>
-    <row r="111" spans="1:5" ht="14.5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="16"/>
       <c r="E111" s="16"/>
     </row>
-    <row r="112" spans="1:5" ht="14.5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="16"/>
       <c r="E112" s="16"/>
     </row>
-    <row r="113" spans="1:5" ht="14.5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="16"/>
       <c r="E113" s="16"/>
     </row>
-    <row r="114" spans="1:5" ht="14.5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="16"/>
       <c r="E114" s="16"/>
     </row>
-    <row r="115" spans="1:5" ht="14.5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="16"/>
       <c r="E115" s="16"/>
     </row>
-    <row r="116" spans="1:5" ht="14.5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="16"/>
       <c r="E116" s="16"/>
     </row>
-    <row r="117" spans="1:5" ht="14.5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="16"/>
       <c r="E117" s="16"/>
     </row>
-    <row r="118" spans="1:5" ht="14.5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="16"/>
       <c r="E118" s="16"/>
     </row>
-    <row r="119" spans="1:5" ht="14.5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="E119" s="16"/>
     </row>
-    <row r="120" spans="1:5" ht="14.5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="16"/>
       <c r="E120" s="16"/>
     </row>
-    <row r="121" spans="1:5" ht="14.5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="16"/>
       <c r="E121" s="16"/>
     </row>
-    <row r="122" spans="1:5" ht="14.5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="16"/>
       <c r="E122" s="16"/>
     </row>
-    <row r="123" spans="1:5" ht="14.5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="16"/>
       <c r="E123" s="16"/>
     </row>
-    <row r="124" spans="1:5" ht="14.5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="16"/>
       <c r="E124" s="16"/>
     </row>
-    <row r="125" spans="1:5" ht="14.5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="16"/>
       <c r="E125" s="16"/>
     </row>
-    <row r="126" spans="1:5" ht="14.5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="E126" s="16"/>
     </row>
-    <row r="127" spans="1:5" ht="14.5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="E127" s="16"/>
     </row>
-    <row r="128" spans="1:5" ht="14.5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="16"/>
       <c r="E128" s="16"/>
     </row>
-    <row r="129" spans="1:5" ht="14.5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="16"/>
       <c r="E129" s="16"/>
     </row>
-    <row r="130" spans="1:5" ht="14.5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="E130" s="16"/>
     </row>
-    <row r="131" spans="1:5" ht="14.5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="E131" s="16"/>
     </row>
-    <row r="132" spans="1:5" ht="14.5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="16"/>
       <c r="E132" s="16"/>
     </row>
-    <row r="133" spans="1:5" ht="14.5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="16"/>
       <c r="E133" s="16"/>
     </row>
-    <row r="134" spans="1:5" ht="14.5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="E134" s="16"/>
     </row>
-    <row r="135" spans="1:5" ht="14.5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="16"/>
       <c r="E135" s="16"/>
     </row>
-    <row r="136" spans="1:5" ht="14.5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="16"/>
       <c r="E136" s="16"/>
     </row>
-    <row r="137" spans="1:5" ht="14.5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="16"/>
       <c r="E137" s="16"/>
     </row>
-    <row r="138" spans="1:5" ht="14.5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
       <c r="E138" s="16"/>
     </row>
-    <row r="139" spans="1:5" ht="14.5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="E139" s="16"/>
     </row>
-    <row r="140" spans="1:5" ht="14.5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="16"/>
       <c r="E140" s="16"/>
     </row>
-    <row r="141" spans="1:5" ht="14.5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="16"/>
       <c r="E141" s="16"/>
     </row>
-    <row r="142" spans="1:5" ht="14.5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="E142" s="16"/>
     </row>
-    <row r="143" spans="1:5" ht="14.5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="E143" s="16"/>
     </row>
-    <row r="144" spans="1:5" ht="14.5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="16"/>
       <c r="E144" s="16"/>
     </row>
-    <row r="145" spans="1:5" ht="14.5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="16"/>
       <c r="E145" s="16"/>
     </row>
-    <row r="146" spans="1:5" ht="14.5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="E146" s="16"/>
     </row>
-    <row r="147" spans="1:5" ht="14.5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="E147" s="16"/>
     </row>
-    <row r="148" spans="1:5" ht="14.5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="16"/>
       <c r="E148" s="16"/>
     </row>
-    <row r="149" spans="1:5" ht="14.5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="16"/>
       <c r="E149" s="16"/>
     </row>
-    <row r="150" spans="1:5" ht="14.5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="16"/>
       <c r="E150" s="16"/>
     </row>
-    <row r="151" spans="1:5" ht="14.5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="16"/>
       <c r="E151" s="16"/>
     </row>
-    <row r="152" spans="1:5" ht="14.5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="16"/>
       <c r="E152" s="16"/>
     </row>
-    <row r="153" spans="1:5" ht="14.5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="16"/>
       <c r="E153" s="16"/>
     </row>
-    <row r="154" spans="1:5" ht="14.5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="E154" s="16"/>
     </row>
-    <row r="155" spans="1:5" ht="14.5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="16"/>
       <c r="E155" s="16"/>
     </row>
-    <row r="156" spans="1:5" ht="14.5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="16"/>
       <c r="E156" s="16"/>
     </row>
-    <row r="157" spans="1:5" ht="14.5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="16"/>
       <c r="E157" s="16"/>
     </row>
-    <row r="158" spans="1:5" ht="14.5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="16"/>
       <c r="E158" s="16"/>
     </row>
-    <row r="159" spans="1:5" ht="14.5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="16"/>
       <c r="E159" s="16"/>
     </row>
-    <row r="160" spans="1:5" ht="14.5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="16"/>
       <c r="E160" s="16"/>
     </row>
-    <row r="161" spans="1:5" ht="14.5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="16"/>
       <c r="E161" s="16"/>
     </row>
-    <row r="162" spans="1:5" ht="14.5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="16"/>
       <c r="E162" s="16"/>
     </row>
-    <row r="163" spans="1:5" ht="14.5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="16"/>
       <c r="E163" s="16"/>
     </row>
-    <row r="164" spans="1:5" ht="14.5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="16"/>
       <c r="E164" s="16"/>
     </row>
-    <row r="165" spans="1:5" ht="14.5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="16"/>
       <c r="E165" s="16"/>
     </row>
-    <row r="166" spans="1:5" ht="14.5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="16"/>
       <c r="E166" s="16"/>
     </row>
-    <row r="167" spans="1:5" ht="14.5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="16"/>
       <c r="E167" s="16"/>
     </row>
-    <row r="168" spans="1:5" ht="14.5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="16"/>
       <c r="E168" s="16"/>
     </row>
-    <row r="169" spans="1:5" ht="14.5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="16"/>
       <c r="E169" s="16"/>
     </row>
-    <row r="170" spans="1:5" ht="14.5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="16"/>
       <c r="E170" s="16"/>
     </row>
-    <row r="171" spans="1:5" ht="14.5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="16"/>
       <c r="E171" s="16"/>
     </row>
-    <row r="172" spans="1:5" ht="14.5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="16"/>
       <c r="E172" s="16"/>
     </row>
-    <row r="173" spans="1:5" ht="14.5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="16"/>
       <c r="E173" s="16"/>
     </row>
-    <row r="174" spans="1:5" ht="14.5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="16"/>
       <c r="E174" s="16"/>
     </row>
-    <row r="175" spans="1:5" ht="14.5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="16"/>
       <c r="E175" s="16"/>
     </row>
-    <row r="176" spans="1:5" ht="14.5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="16"/>
       <c r="E176" s="16"/>
     </row>
-    <row r="177" spans="1:5" ht="14.5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="16"/>
       <c r="E177" s="16"/>
     </row>
-    <row r="178" spans="1:5" ht="14.5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="16"/>
       <c r="E178" s="16"/>
     </row>
-    <row r="179" spans="1:5" ht="14.5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="16"/>
       <c r="E179" s="16"/>
     </row>
-    <row r="180" spans="1:5" ht="14.5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="16"/>
       <c r="E180" s="16"/>
     </row>
-    <row r="181" spans="1:5" ht="14.5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="16"/>
       <c r="E181" s="16"/>
     </row>
-    <row r="182" spans="1:5" ht="14.5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="16"/>
       <c r="E182" s="16"/>
     </row>
-    <row r="183" spans="1:5" ht="14.5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="16"/>
       <c r="E183" s="16"/>
     </row>
-    <row r="184" spans="1:5" ht="14.5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="16"/>
       <c r="E184" s="16"/>
     </row>
-    <row r="185" spans="1:5" ht="14.5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="16"/>
       <c r="E185" s="16"/>
     </row>
-    <row r="186" spans="1:5" ht="14.5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="16"/>
       <c r="E186" s="16"/>
     </row>
-    <row r="187" spans="1:5" ht="14.5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="16"/>
       <c r="E187" s="16"/>
     </row>
-    <row r="188" spans="1:5" ht="14.5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="16"/>
       <c r="E188" s="16"/>
     </row>
-    <row r="189" spans="1:5" ht="14.5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="16"/>
       <c r="E189" s="16"/>
     </row>
-    <row r="190" spans="1:5" ht="14.5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="16"/>
       <c r="E190" s="16"/>
     </row>
-    <row r="191" spans="1:5" ht="14.5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="16"/>
       <c r="E191" s="16"/>
     </row>
-    <row r="192" spans="1:5" ht="14.5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="16"/>
       <c r="E192" s="16"/>
     </row>
-    <row r="193" spans="1:5" ht="14.5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="16"/>
       <c r="E193" s="16"/>
     </row>
-    <row r="194" spans="1:5" ht="14.5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="16"/>
       <c r="E194" s="16"/>
     </row>
-    <row r="195" spans="1:5" ht="14.5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="16"/>
       <c r="E195" s="16"/>
     </row>
-    <row r="196" spans="1:5" ht="14.5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="16"/>
       <c r="E196" s="16"/>
     </row>
@@ -2986,43 +2825,43 @@
     <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0463B4E7-0F46-4E49-9E42-9788876E21BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0463B4E7-0F46-4E49-9E42-9788876E21BA}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Y199"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5714285714286" customWidth="1"/>
-    <col min="5" max="6" width="22.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="22.2857142857143" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.2857142857143" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.4285714285714" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.85714285714286" customWidth="1"/>
-    <col min="13" max="13" width="10.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="86.2857142857143" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.2857142857143" customWidth="1"/>
-    <col min="18" max="18" width="44.8571428571429" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5714285714286" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.14285714285714" customWidth="1"/>
-    <col min="23" max="23" width="10.1428571428571" customWidth="1"/>
-    <col min="24" max="24" width="75.8571428571429" customWidth="1"/>
-    <col min="27" max="27" width="10.1428571428571" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="5" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="86.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.28515625" customWidth="1"/>
+    <col min="18" max="18" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.140625" customWidth="1"/>
+    <col min="23" max="23" width="10.140625" customWidth="1"/>
+    <col min="24" max="24" width="75.85546875" customWidth="1"/>
+    <col min="27" max="27" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.5">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="16"/>
       <c r="G1" s="16"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:25" ht="126" customHeight="1">
+    <row r="2" spans="1:25" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
@@ -3061,7 +2900,7 @@
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
     </row>
-    <row r="3" spans="1:25" ht="72" customHeight="1">
+    <row r="3" spans="1:25" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>12</v>
       </c>
@@ -3098,7 +2937,7 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" spans="1:25" ht="14.5">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -3125,7 +2964,7 @@
       <c r="X4" s="16"/>
       <c r="Y4" s="16"/>
     </row>
-    <row r="5" spans="1:23" ht="14.5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="B5" s="9" t="s">
         <v>1</v>
@@ -3139,7 +2978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15" thickBot="1">
+    <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
       <c r="B6" s="11" t="s">
         <v>0</v>
@@ -3186,7 +3025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="14.5">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" t="str">
         <f>IF(C7="","","PRC_GMAP")</f>
@@ -3251,11 +3090,11 @@
         <v>,</v>
       </c>
       <c r="W7" t="str">
-        <f t="shared" si="0" ref="W7:W13">IF(X7=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="W7:W13" si="0">IF(X7=" ","","SFCmd_bot")</f>
         <v>SFCmd_bot</v>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="1" ref="X7:X13">_xlfn.CONCAT(R7:S7)&amp;" "&amp;_xlfn.CONCAT(T7:U7)</f>
+        <f t="shared" ref="X7:X13" si="1">_xlfn.CONCAT(R7:S7)&amp;" "&amp;_xlfn.CONCAT(T7:U7)</f>
         <v>SET comgroupTIMESreport 'comgroup TIMESreport'/ NRG_ELC 'Electricity',</v>
       </c>
       <c r="Y7">
@@ -3263,10 +3102,10 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="14.5">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" t="str">
-        <f t="shared" si="2" ref="B8:B71">IF(C8="","","PRC_GMAP")</f>
+        <f t="shared" ref="B8:B71" si="2">IF(C8="","","PRC_GMAP")</f>
         <v>PRC_GMAP</v>
       </c>
       <c r="C8" t="str">
@@ -3274,7 +3113,7 @@
         <v>GW</v>
       </c>
       <c r="D8">
-        <f t="shared" si="3" ref="D8:D71">IF(C8="","",1)</f>
+        <f t="shared" ref="D8:D71" si="3">IF(C8="","",1)</f>
         <v>1</v>
       </c>
       <c r="E8" t="str">
@@ -3299,11 +3138,11 @@
         <v>,</v>
       </c>
       <c r="M8" t="str">
-        <f t="shared" si="4" ref="M8:M71">IF(N8=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="M8:M71" si="4">IF(N8=" ","","SFCmd_bot")</f>
         <v>SFCmd_bot</v>
       </c>
       <c r="N8" s="13" t="str">
-        <f t="shared" si="5" ref="N8:N71">_xlfn.CONCAT(H8:I8)&amp;" "&amp;_xlfn.CONCAT(J8:K8)</f>
+        <f t="shared" ref="N8:N71" si="5">_xlfn.CONCAT(H8:I8)&amp;" "&amp;_xlfn.CONCAT(J8:K8)</f>
         <v>GW 'GW',</v>
       </c>
       <c r="O8">
@@ -3336,11 +3175,11 @@
         <v>NRG_GAS 'Gas',</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="6" ref="Y8:Y13">IF(W8="","",Y7+1)</f>
+        <f t="shared" ref="Y8:Y13" si="6">IF(W8="","",Y7+1)</f>
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="14.5">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" t="str">
         <f t="shared" si="2"/>
@@ -3384,7 +3223,7 @@
         <v>Mta 'Million ton a year',</v>
       </c>
       <c r="O9">
-        <f t="shared" si="7" ref="O9:O72">IF(M9="","",O8+1)</f>
+        <f t="shared" ref="O9:O72" si="7">IF(M9="","",O8+1)</f>
         <v>3</v>
       </c>
       <c r="Q9" s="16"/>
@@ -3417,7 +3256,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="14.5">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" t="str">
         <f t="shared" si="2"/>
@@ -3494,7 +3333,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="14.5">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" t="str">
         <f t="shared" si="2"/>
@@ -3571,7 +3410,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="14.5">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" t="str">
         <f t="shared" si="2"/>
@@ -3648,7 +3487,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="14.5">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" t="str">
         <f t="shared" si="2"/>
@@ -3725,7 +3564,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="13.5" customHeight="1">
+    <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" t="str">
         <f t="shared" si="2"/>
@@ -3794,7 +3633,7 @@
         <v>SFCmd_bot</v>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="8" ref="X14:X71">_xlfn.CONCAT(R14:S14)&amp;" "&amp;_xlfn.CONCAT(T14:U14)</f>
+        <f t="shared" ref="X14:X71" si="8">_xlfn.CONCAT(R14:S14)&amp;" "&amp;_xlfn.CONCAT(T14:U14)</f>
         <v>ENV_CO2 'GHG-emission',</v>
       </c>
       <c r="Y14">
@@ -3802,7 +3641,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="14.5">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" t="str">
         <f t="shared" si="2"/>
@@ -3867,7 +3706,7 @@
         <v>/ ;,</v>
       </c>
       <c r="W15" t="str">
-        <f t="shared" si="9" ref="W15:W78">IF(X15=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="W15:W78" si="9">IF(X15=" ","","SFCmd_bot")</f>
         <v>SFCmd_bot</v>
       </c>
       <c r="X15" t="str">
@@ -3875,11 +3714,11 @@
         <v>DEM_COM 'Demand commodity'/ ;,</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="10" ref="Y15:Y78">IF(W15="","",Y14+1)</f>
+        <f t="shared" ref="Y15:Y78" si="10">IF(W15="","",Y14+1)</f>
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="14.5">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" t="str">
         <f t="shared" si="2"/>
@@ -3956,7 +3795,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="14.5">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" t="str">
         <f t="shared" si="2"/>
@@ -4033,7 +3872,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="14.5">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" t="str">
         <f t="shared" si="2"/>
@@ -4110,7 +3949,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="14.5">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" t="str">
         <f t="shared" si="2"/>
@@ -4187,7 +4026,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="14.5">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" t="str">
         <f t="shared" si="2"/>
@@ -4264,7 +4103,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="14.5">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" t="str">
         <f t="shared" si="2"/>
@@ -4341,7 +4180,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="14.5">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" t="str">
         <f t="shared" si="2"/>
@@ -4418,7 +4257,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="14.5">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" t="str">
         <f t="shared" si="2"/>
@@ -4495,7 +4334,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="14.5">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" t="str">
         <f t="shared" si="2"/>
@@ -4572,7 +4411,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="14.5">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" t="str">
         <f t="shared" si="2"/>
@@ -4649,7 +4488,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="14.5">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" t="str">
         <f t="shared" si="2"/>
@@ -4726,7 +4565,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="14.5">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" t="str">
         <f t="shared" si="2"/>
@@ -4803,7 +4642,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="14.5">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" t="str">
         <f t="shared" si="2"/>
@@ -4880,7 +4719,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="14.5">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" t="str">
         <f t="shared" si="2"/>
@@ -4957,7 +4796,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="14.5">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" t="str">
         <f t="shared" si="2"/>
@@ -5034,7 +4873,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="14.5">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" t="str">
         <f t="shared" si="2"/>
@@ -5111,7 +4950,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="14.5">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" t="str">
         <f t="shared" si="2"/>
@@ -5188,7 +5027,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="12.75" customHeight="1">
+    <row r="33" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" t="str">
         <f t="shared" si="2"/>
@@ -5265,7 +5104,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="14.5">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" t="str">
         <f t="shared" si="2"/>
@@ -5342,7 +5181,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="14.5">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" t="str">
         <f t="shared" si="2"/>
@@ -5419,7 +5258,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="14.5">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" t="str">
         <f t="shared" si="2"/>
@@ -5496,7 +5335,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="14.5">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" t="str">
         <f t="shared" si="2"/>
@@ -5573,7 +5412,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="14.5">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" t="str">
         <f t="shared" si="2"/>
@@ -5650,7 +5489,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="14.5">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" t="str">
         <f t="shared" si="2"/>
@@ -5727,7 +5566,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="14.5">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" t="str">
         <f t="shared" si="2"/>
@@ -5804,7 +5643,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="14.5">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" t="str">
         <f t="shared" si="2"/>
@@ -5881,7 +5720,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="14.5">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" t="str">
         <f t="shared" si="2"/>
@@ -5958,7 +5797,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="14.5">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" t="str">
         <f t="shared" si="2"/>
@@ -6035,7 +5874,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="14.5">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" t="str">
         <f t="shared" si="2"/>
@@ -6112,7 +5951,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="14.5">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" t="str">
         <f t="shared" si="2"/>
@@ -6189,7 +6028,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="14.5">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" t="str">
         <f t="shared" si="2"/>
@@ -6266,7 +6105,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="14.5">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" t="str">
         <f t="shared" si="2"/>
@@ -6343,7 +6182,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="14.5">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" t="str">
         <f t="shared" si="2"/>
@@ -6420,7 +6259,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="14.5">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
       <c r="B49" t="str">
         <f t="shared" si="2"/>
@@ -6497,7 +6336,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="14.5">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" t="str">
         <f t="shared" si="2"/>
@@ -6574,7 +6413,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="14.5">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" t="str">
         <f t="shared" si="2"/>
@@ -6651,7 +6490,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="14.5">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" t="str">
         <f t="shared" si="2"/>
@@ -6728,7 +6567,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="14.5">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
       <c r="B53" t="str">
         <f t="shared" si="2"/>
@@ -6805,7 +6644,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="14.5">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" t="str">
         <f t="shared" si="2"/>
@@ -6882,7 +6721,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="14.5">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="16"/>
       <c r="B55" t="str">
         <f t="shared" si="2"/>
@@ -6959,7 +6798,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="14.5">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" t="str">
         <f t="shared" si="2"/>
@@ -7036,7 +6875,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="14.5">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" t="str">
         <f t="shared" si="2"/>
@@ -7113,7 +6952,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="14.5">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" t="str">
         <f t="shared" si="2"/>
@@ -7190,7 +7029,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="14.5">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" t="str">
         <f t="shared" si="2"/>
@@ -7267,7 +7106,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="14.5">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" t="str">
         <f t="shared" si="2"/>
@@ -7344,7 +7183,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="14.5">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
       <c r="B61" t="str">
         <f t="shared" si="2"/>
@@ -7421,7 +7260,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="14.5">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="16"/>
       <c r="B62" t="str">
         <f t="shared" si="2"/>
@@ -7498,7 +7337,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="14.5">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="16"/>
       <c r="B63" t="str">
         <f t="shared" si="2"/>
@@ -7575,7 +7414,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="14.5">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
       <c r="B64" t="str">
         <f t="shared" si="2"/>
@@ -7652,7 +7491,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="14.5">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="16"/>
       <c r="B65" t="str">
         <f t="shared" si="2"/>
@@ -7729,7 +7568,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="14.5">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
       <c r="B66" t="str">
         <f t="shared" si="2"/>
@@ -7806,7 +7645,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="14.5">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="16"/>
       <c r="B67" t="str">
         <f t="shared" si="2"/>
@@ -7883,7 +7722,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="14.5">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="16"/>
       <c r="B68" t="str">
         <f t="shared" si="2"/>
@@ -7960,7 +7799,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="14.5">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="16"/>
       <c r="B69" t="str">
         <f t="shared" si="2"/>
@@ -8037,7 +7876,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="14.5">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="16"/>
       <c r="B70" t="str">
         <f t="shared" si="2"/>
@@ -8114,7 +7953,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="14.5">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="16"/>
       <c r="B71" t="str">
         <f t="shared" si="2"/>
@@ -8191,10 +8030,10 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="14.5">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="B72" t="str">
-        <f t="shared" si="11" ref="B72:B135">IF(C72="","","PRC_GMAP")</f>
+        <f t="shared" ref="B72:B135" si="11">IF(C72="","","PRC_GMAP")</f>
         <v/>
       </c>
       <c r="C72" t="str">
@@ -8202,7 +8041,7 @@
         <v/>
       </c>
       <c r="D72" t="str">
-        <f t="shared" si="12" ref="D72:D135">IF(C72="","",1)</f>
+        <f t="shared" ref="D72:D135" si="12">IF(C72="","",1)</f>
         <v/>
       </c>
       <c r="E72" t="str">
@@ -8227,11 +8066,11 @@
         <v/>
       </c>
       <c r="M72" t="str">
-        <f t="shared" si="13" ref="M72:M135">IF(N72=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="M72:M135" si="13">IF(N72=" ","","SFCmd_bot")</f>
         <v/>
       </c>
       <c r="N72" s="13" t="str">
-        <f t="shared" si="14" ref="N72:N135">_xlfn.CONCAT(H72:I72)&amp;" "&amp;_xlfn.CONCAT(J72:K72)</f>
+        <f t="shared" ref="N72:N135" si="14">_xlfn.CONCAT(H72:I72)&amp;" "&amp;_xlfn.CONCAT(J72:K72)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="O72" t="str">
@@ -8260,7 +8099,7 @@
         <v/>
       </c>
       <c r="X72" t="str">
-        <f t="shared" si="15" ref="X72:X135">_xlfn.CONCAT(R72:S72)&amp;" "&amp;_xlfn.CONCAT(T72:U72)</f>
+        <f t="shared" ref="X72:X135" si="15">_xlfn.CONCAT(R72:S72)&amp;" "&amp;_xlfn.CONCAT(T72:U72)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Y72" t="str">
@@ -8268,7 +8107,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="14.5">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="16"/>
       <c r="B73" t="str">
         <f t="shared" si="11"/>
@@ -8312,7 +8151,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="O73" t="str">
-        <f t="shared" si="16" ref="O73:O136">IF(M73="","",O72+1)</f>
+        <f t="shared" ref="O73:O136" si="16">IF(M73="","",O72+1)</f>
         <v/>
       </c>
       <c r="Q73" s="16"/>
@@ -8345,7 +8184,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="14.5">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="16"/>
       <c r="B74" t="str">
         <f t="shared" si="11"/>
@@ -8422,7 +8261,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="14.5">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="16"/>
       <c r="B75" t="str">
         <f t="shared" si="11"/>
@@ -8499,7 +8338,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="14.5">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="B76" t="str">
         <f t="shared" si="11"/>
@@ -8576,7 +8415,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="14.5">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
       <c r="B77" t="str">
         <f t="shared" si="11"/>
@@ -8653,7 +8492,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="14.5">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
       <c r="B78" t="str">
         <f t="shared" si="11"/>
@@ -8730,7 +8569,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="14.5">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="16"/>
       <c r="B79" t="str">
         <f t="shared" si="11"/>
@@ -8795,7 +8634,7 @@
         <v/>
       </c>
       <c r="W79" t="str">
-        <f t="shared" si="17" ref="W79:W142">IF(X79=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="W79:W142" si="17">IF(X79=" ","","SFCmd_bot")</f>
         <v/>
       </c>
       <c r="X79" t="str">
@@ -8803,11 +8642,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="Y79" t="str">
-        <f t="shared" si="18" ref="Y79:Y142">IF(W79="","",Y78+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:25" ht="14.5">
+        <f t="shared" ref="Y79:Y142" si="18">IF(W79="","",Y78+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="16"/>
       <c r="B80" t="str">
         <f t="shared" si="11"/>
@@ -8884,7 +8723,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="14.5">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="16"/>
       <c r="B81" t="str">
         <f t="shared" si="11"/>
@@ -8961,7 +8800,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="14.5">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="B82" t="str">
         <f t="shared" si="11"/>
@@ -9038,7 +8877,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="14.5">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="16"/>
       <c r="B83" t="str">
         <f t="shared" si="11"/>
@@ -9115,7 +8954,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="14.5">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="16"/>
       <c r="B84" t="str">
         <f t="shared" si="11"/>
@@ -9192,7 +9031,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="14.5">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="16"/>
       <c r="B85" t="str">
         <f t="shared" si="11"/>
@@ -9269,7 +9108,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="14.5">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="16"/>
       <c r="B86" t="str">
         <f t="shared" si="11"/>
@@ -9346,7 +9185,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="14.5">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="16"/>
       <c r="B87" t="str">
         <f t="shared" si="11"/>
@@ -9423,7 +9262,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="14.5">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="16"/>
       <c r="B88" t="str">
         <f t="shared" si="11"/>
@@ -9500,7 +9339,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="14.5">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="16"/>
       <c r="B89" t="str">
         <f t="shared" si="11"/>
@@ -9577,7 +9416,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="14.5">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="16"/>
       <c r="B90" t="str">
         <f t="shared" si="11"/>
@@ -9654,7 +9493,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="14.5">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="16"/>
       <c r="B91" t="str">
         <f t="shared" si="11"/>
@@ -9731,7 +9570,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="14.5">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="16"/>
       <c r="B92" t="str">
         <f t="shared" si="11"/>
@@ -9808,7 +9647,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="14.5">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="16"/>
       <c r="B93" t="str">
         <f t="shared" si="11"/>
@@ -9885,7 +9724,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="14.5">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="16"/>
       <c r="B94" t="str">
         <f t="shared" si="11"/>
@@ -9962,7 +9801,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="14.5">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="16"/>
       <c r="B95" t="str">
         <f t="shared" si="11"/>
@@ -10039,7 +9878,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="14.5">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="16"/>
       <c r="B96" t="str">
         <f t="shared" si="11"/>
@@ -10116,7 +9955,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="14.5">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
       <c r="B97" t="str">
         <f t="shared" si="11"/>
@@ -10193,7 +10032,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="14.5">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="16"/>
       <c r="B98" t="str">
         <f t="shared" si="11"/>
@@ -10270,7 +10109,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="14.5">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="16"/>
       <c r="B99" t="str">
         <f t="shared" si="11"/>
@@ -10347,7 +10186,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="14.5">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="16"/>
       <c r="B100" t="str">
         <f t="shared" si="11"/>
@@ -10424,7 +10263,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="14.5">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="16"/>
       <c r="B101" t="str">
         <f t="shared" si="11"/>
@@ -10501,7 +10340,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="14.5">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="16"/>
       <c r="B102" t="str">
         <f t="shared" si="11"/>
@@ -10578,7 +10417,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="14.5">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="16"/>
       <c r="B103" t="str">
         <f t="shared" si="11"/>
@@ -10655,7 +10494,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="14.5">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="16"/>
       <c r="B104" t="str">
         <f t="shared" si="11"/>
@@ -10732,7 +10571,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="14.5">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="16"/>
       <c r="B105" t="str">
         <f t="shared" si="11"/>
@@ -10809,7 +10648,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="14.5">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="16"/>
       <c r="B106" t="str">
         <f t="shared" si="11"/>
@@ -10886,7 +10725,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="14.5">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="16"/>
       <c r="B107" t="str">
         <f t="shared" si="11"/>
@@ -10963,7 +10802,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="14.5">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="16"/>
       <c r="B108" t="str">
         <f t="shared" si="11"/>
@@ -11040,7 +10879,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="14.5">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="16"/>
       <c r="B109" t="str">
         <f t="shared" si="11"/>
@@ -11117,7 +10956,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="14.5">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="16"/>
       <c r="B110" t="str">
         <f t="shared" si="11"/>
@@ -11194,7 +11033,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="14.5">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="16"/>
       <c r="B111" t="str">
         <f t="shared" si="11"/>
@@ -11271,7 +11110,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="14.5">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="16"/>
       <c r="B112" t="str">
         <f t="shared" si="11"/>
@@ -11348,7 +11187,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="14.5">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="16"/>
       <c r="B113" t="str">
         <f t="shared" si="11"/>
@@ -11425,7 +11264,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="14.5">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="16"/>
       <c r="B114" t="str">
         <f t="shared" si="11"/>
@@ -11502,7 +11341,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="14.5">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="16"/>
       <c r="B115" t="str">
         <f t="shared" si="11"/>
@@ -11579,7 +11418,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="14.5">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="16"/>
       <c r="B116" t="str">
         <f t="shared" si="11"/>
@@ -11656,7 +11495,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="14.5">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" s="16"/>
       <c r="B117" t="str">
         <f t="shared" si="11"/>
@@ -11733,7 +11572,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="14.5">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" s="16"/>
       <c r="B118" t="str">
         <f t="shared" si="11"/>
@@ -11810,7 +11649,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="14.5">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="16"/>
       <c r="B119" t="str">
         <f t="shared" si="11"/>
@@ -11887,7 +11726,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="14.5">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" s="16"/>
       <c r="B120" t="str">
         <f t="shared" si="11"/>
@@ -11964,7 +11803,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="14.5">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="16"/>
       <c r="B121" t="str">
         <f t="shared" si="11"/>
@@ -12041,7 +11880,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="14.5">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="16"/>
       <c r="B122" t="str">
         <f t="shared" si="11"/>
@@ -12118,7 +11957,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="14.5">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="16"/>
       <c r="B123" t="str">
         <f t="shared" si="11"/>
@@ -12195,7 +12034,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="14.5">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="16"/>
       <c r="B124" t="str">
         <f t="shared" si="11"/>
@@ -12272,7 +12111,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="14.5">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="16"/>
       <c r="B125" t="str">
         <f t="shared" si="11"/>
@@ -12349,7 +12188,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="14.5">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="16"/>
       <c r="B126" t="str">
         <f t="shared" si="11"/>
@@ -12426,7 +12265,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="14.5">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="16"/>
       <c r="B127" t="str">
         <f t="shared" si="11"/>
@@ -12503,7 +12342,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="14.5">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" s="16"/>
       <c r="B128" t="str">
         <f t="shared" si="11"/>
@@ -12580,7 +12419,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="14.5">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" s="16"/>
       <c r="B129" t="str">
         <f t="shared" si="11"/>
@@ -12657,7 +12496,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="14.5">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" s="16"/>
       <c r="B130" t="str">
         <f t="shared" si="11"/>
@@ -12734,7 +12573,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="14.5">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" s="16"/>
       <c r="B131" t="str">
         <f t="shared" si="11"/>
@@ -12811,7 +12650,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="14.5">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" s="16"/>
       <c r="B132" t="str">
         <f t="shared" si="11"/>
@@ -12888,7 +12727,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="14.5">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" s="16"/>
       <c r="B133" t="str">
         <f t="shared" si="11"/>
@@ -12965,7 +12804,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="14.5">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" s="16"/>
       <c r="B134" t="str">
         <f t="shared" si="11"/>
@@ -13042,7 +12881,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="14.5">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" s="16"/>
       <c r="B135" t="str">
         <f t="shared" si="11"/>
@@ -13119,10 +12958,10 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="14.5">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" s="16"/>
       <c r="B136" t="str">
-        <f t="shared" si="19" ref="B136:B197">IF(C136="","","PRC_GMAP")</f>
+        <f t="shared" ref="B136:B197" si="19">IF(C136="","","PRC_GMAP")</f>
         <v/>
       </c>
       <c r="C136" t="str">
@@ -13130,7 +12969,7 @@
         <v/>
       </c>
       <c r="D136" t="str">
-        <f t="shared" si="20" ref="D136:D197">IF(C136="","",1)</f>
+        <f t="shared" ref="D136:D197" si="20">IF(C136="","",1)</f>
         <v/>
       </c>
       <c r="E136" t="str">
@@ -13155,11 +12994,11 @@
         <v/>
       </c>
       <c r="M136" t="str">
-        <f t="shared" si="21" ref="M136:M197">IF(N136=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="M136:M197" si="21">IF(N136=" ","","SFCmd_bot")</f>
         <v/>
       </c>
       <c r="N136" s="13" t="str">
-        <f t="shared" si="22" ref="N136:N197">_xlfn.CONCAT(H136:I136)&amp;" "&amp;_xlfn.CONCAT(J136:K136)</f>
+        <f t="shared" ref="N136:N197" si="22">_xlfn.CONCAT(H136:I136)&amp;" "&amp;_xlfn.CONCAT(J136:K136)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="O136" t="str">
@@ -13188,7 +13027,7 @@
         <v/>
       </c>
       <c r="X136" t="str">
-        <f t="shared" si="23" ref="X136:X197">_xlfn.CONCAT(R136:S136)&amp;" "&amp;_xlfn.CONCAT(T136:U136)</f>
+        <f t="shared" ref="X136:X197" si="23">_xlfn.CONCAT(R136:S136)&amp;" "&amp;_xlfn.CONCAT(T136:U136)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Y136" t="str">
@@ -13196,7 +13035,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="14.5">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="16"/>
       <c r="B137" t="str">
         <f t="shared" si="19"/>
@@ -13240,7 +13079,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="O137" t="str">
-        <f t="shared" si="24" ref="O137:O197">IF(M137="","",O136+1)</f>
+        <f t="shared" ref="O137:O197" si="24">IF(M137="","",O136+1)</f>
         <v/>
       </c>
       <c r="Q137" s="16"/>
@@ -13273,7 +13112,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="14.5">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" s="16"/>
       <c r="B138" t="str">
         <f t="shared" si="19"/>
@@ -13350,7 +13189,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="14.5">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="16"/>
       <c r="B139" t="str">
         <f t="shared" si="19"/>
@@ -13427,7 +13266,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="14.5">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" s="16"/>
       <c r="B140" t="str">
         <f t="shared" si="19"/>
@@ -13504,7 +13343,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="14.5">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="16"/>
       <c r="B141" t="str">
         <f t="shared" si="19"/>
@@ -13581,7 +13420,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="14.5">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" s="16"/>
       <c r="B142" t="str">
         <f t="shared" si="19"/>
@@ -13658,7 +13497,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="14.5">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="16"/>
       <c r="B143" t="str">
         <f t="shared" si="19"/>
@@ -13723,7 +13562,7 @@
         <v/>
       </c>
       <c r="W143" t="str">
-        <f t="shared" si="25" ref="W143:W197">IF(X143=" ","","SFCmd_bot")</f>
+        <f t="shared" ref="W143:W197" si="25">IF(X143=" ","","SFCmd_bot")</f>
         <v/>
       </c>
       <c r="X143" t="str">
@@ -13731,11 +13570,11 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="Y143" t="str">
-        <f t="shared" si="26" ref="Y143:Y197">IF(W143="","",Y142+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:25" ht="14.5">
+        <f t="shared" ref="Y143:Y197" si="26">IF(W143="","",Y142+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" s="16"/>
       <c r="B144" t="str">
         <f t="shared" si="19"/>
@@ -13812,7 +13651,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="14.5">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="16"/>
       <c r="B145" t="str">
         <f t="shared" si="19"/>
@@ -13889,7 +13728,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="14.5">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="16"/>
       <c r="B146" t="str">
         <f t="shared" si="19"/>
@@ -13966,7 +13805,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="14.5">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="16"/>
       <c r="B147" t="str">
         <f t="shared" si="19"/>
@@ -14043,7 +13882,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="14.5">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="16"/>
       <c r="B148" t="str">
         <f t="shared" si="19"/>
@@ -14120,7 +13959,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="14.5">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="16"/>
       <c r="B149" t="str">
         <f t="shared" si="19"/>
@@ -14197,7 +14036,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="14.5">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="16"/>
       <c r="B150" t="str">
         <f t="shared" si="19"/>
@@ -14274,7 +14113,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="14.5">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="16"/>
       <c r="B151" t="str">
         <f t="shared" si="19"/>
@@ -14351,7 +14190,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="14.5">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="16"/>
       <c r="B152" t="str">
         <f t="shared" si="19"/>
@@ -14428,7 +14267,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="14.5">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="16"/>
       <c r="B153" t="str">
         <f t="shared" si="19"/>
@@ -14505,7 +14344,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="14.5">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="16"/>
       <c r="B154" t="str">
         <f t="shared" si="19"/>
@@ -14582,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="14.5">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="16"/>
       <c r="B155" t="str">
         <f t="shared" si="19"/>
@@ -14659,7 +14498,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="14.5">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="16"/>
       <c r="B156" t="str">
         <f t="shared" si="19"/>
@@ -14736,7 +14575,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="14.5">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="16"/>
       <c r="B157" t="str">
         <f t="shared" si="19"/>
@@ -14813,7 +14652,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="14.5">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="16"/>
       <c r="B158" t="str">
         <f t="shared" si="19"/>
@@ -14890,7 +14729,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="14.5">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="16"/>
       <c r="B159" t="str">
         <f t="shared" si="19"/>
@@ -14967,7 +14806,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="14.5">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="16"/>
       <c r="B160" t="str">
         <f t="shared" si="19"/>
@@ -15044,7 +14883,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="14.5">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="16"/>
       <c r="B161" t="str">
         <f t="shared" si="19"/>
@@ -15121,7 +14960,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="14.5">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" s="16"/>
       <c r="B162" t="str">
         <f t="shared" si="19"/>
@@ -15198,7 +15037,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="14.5">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" s="16"/>
       <c r="B163" t="str">
         <f t="shared" si="19"/>
@@ -15275,7 +15114,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="14.5">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" s="16"/>
       <c r="B164" t="str">
         <f t="shared" si="19"/>
@@ -15352,7 +15191,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="14.5">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="16"/>
       <c r="B165" t="str">
         <f t="shared" si="19"/>
@@ -15429,7 +15268,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="14.5">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="16"/>
       <c r="B166" t="str">
         <f t="shared" si="19"/>
@@ -15506,7 +15345,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="14.5">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="16"/>
       <c r="B167" t="str">
         <f t="shared" si="19"/>
@@ -15583,7 +15422,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="14.5">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="16"/>
       <c r="B168" t="str">
         <f t="shared" si="19"/>
@@ -15660,7 +15499,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="14.5">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="16"/>
       <c r="B169" t="str">
         <f t="shared" si="19"/>
@@ -15737,7 +15576,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="14.5">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="16"/>
       <c r="B170" t="str">
         <f t="shared" si="19"/>
@@ -15814,7 +15653,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="14.5">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" s="16"/>
       <c r="B171" t="str">
         <f t="shared" si="19"/>
@@ -15891,7 +15730,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="14.5">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="16"/>
       <c r="B172" t="str">
         <f t="shared" si="19"/>
@@ -15968,7 +15807,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="14.5">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="16"/>
       <c r="B173" t="str">
         <f t="shared" si="19"/>
@@ -16045,7 +15884,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="14.5">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" s="16"/>
       <c r="B174" t="str">
         <f t="shared" si="19"/>
@@ -16122,7 +15961,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="14.5">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="16"/>
       <c r="B175" t="str">
         <f t="shared" si="19"/>
@@ -16199,7 +16038,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="14.5">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="16"/>
       <c r="B176" t="str">
         <f t="shared" si="19"/>
@@ -16276,7 +16115,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="14.5">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" s="16"/>
       <c r="B177" t="str">
         <f t="shared" si="19"/>
@@ -16353,7 +16192,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="14.5">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" s="16"/>
       <c r="B178" t="str">
         <f t="shared" si="19"/>
@@ -16430,7 +16269,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="14.5">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" s="16"/>
       <c r="B179" t="str">
         <f t="shared" si="19"/>
@@ -16507,7 +16346,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="14.5">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" s="16"/>
       <c r="B180" t="str">
         <f t="shared" si="19"/>
@@ -16584,7 +16423,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="14.5">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" s="16"/>
       <c r="B181" t="str">
         <f t="shared" si="19"/>
@@ -16661,7 +16500,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="14.5">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" s="16"/>
       <c r="B182" t="str">
         <f t="shared" si="19"/>
@@ -16738,7 +16577,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="14.5">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" s="16"/>
       <c r="B183" t="str">
         <f t="shared" si="19"/>
@@ -16815,7 +16654,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="14.5">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" s="16"/>
       <c r="B184" t="str">
         <f t="shared" si="19"/>
@@ -16892,7 +16731,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="14.5">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" s="16"/>
       <c r="B185" t="str">
         <f t="shared" si="19"/>
@@ -16969,7 +16808,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="14.5">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" s="16"/>
       <c r="B186" t="str">
         <f t="shared" si="19"/>
@@ -17046,7 +16885,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="14.5">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" s="16"/>
       <c r="B187" t="str">
         <f t="shared" si="19"/>
@@ -17123,7 +16962,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="14.5">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" s="16"/>
       <c r="B188" t="str">
         <f t="shared" si="19"/>
@@ -17200,7 +17039,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="14.5">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" s="16"/>
       <c r="B189" t="str">
         <f t="shared" si="19"/>
@@ -17277,7 +17116,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="14.5">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" s="16"/>
       <c r="B190" t="str">
         <f t="shared" si="19"/>
@@ -17354,7 +17193,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="14.5">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" s="16"/>
       <c r="B191" t="str">
         <f t="shared" si="19"/>
@@ -17431,7 +17270,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="14.5">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" s="16"/>
       <c r="B192" t="str">
         <f t="shared" si="19"/>
@@ -17508,7 +17347,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="14.5">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="16"/>
       <c r="B193" t="str">
         <f t="shared" si="19"/>
@@ -17585,7 +17424,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="14.5">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" s="16"/>
       <c r="B194" t="str">
         <f t="shared" si="19"/>
@@ -17662,7 +17501,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="14.5">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" s="16"/>
       <c r="B195" t="str">
         <f t="shared" si="19"/>
@@ -17739,7 +17578,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="14.5">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" s="16"/>
       <c r="B196" t="str">
         <f t="shared" si="19"/>
@@ -17816,7 +17655,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="14.5">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" s="16"/>
       <c r="B197" t="str">
         <f t="shared" si="19"/>
@@ -17893,10 +17732,10 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="14:14" ht="14.5">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N198" s="14"/>
     </row>
-    <row r="199" spans="14:14" ht="14.5">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N199" s="14"/>
     </row>
   </sheetData>
@@ -17915,23 +17754,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C582F1-B24B-49CC-AFBB-748FAAC8AD46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C582F1-B24B-49CC-AFBB-748FAAC8AD46}">
   <dimension ref="B2:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.4285714285714" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="6.28571428571429" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="71.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="71.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="14.5">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="14.5">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
@@ -17945,10 +17784,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14.5">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="str">
-        <f>IF(G4="Yes","RFCmd_FLAGS","*")</f>
-        <v>RFCmd_FLAGS</v>
+        <f>IF(G4="Yes","RFCmd_F","*")</f>
+        <v>RFCmd_F</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>23</v>
@@ -17960,23 +17799,37 @@
         <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="14.5">
-      <c r="B5" s="21"/>
-      <c r="C5" s="13"/>
-    </row>
-    <row r="6" spans="2:3" ht="14.5">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="21" t="str">
+        <f>IF(G5="Yes","RFCmd_F","*")</f>
+        <v>RFCmd_F</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="21"/>
       <c r="C6" s="13"/>
     </row>
-    <row r="7" spans="2:2" ht="14.5">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14.5">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="22" t="s">
         <v>0</v>
       </c>
@@ -17987,40 +17840,40 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="14.5">
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="str">
-        <f t="shared" si="0" ref="B9:B15">IF(G9="Yes","RPT_OPT","*")</f>
+        <f t="shared" ref="B9:B15" si="0">IF(G9="Yes","RPT_OPT","*")</f>
         <v>*</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="24">
         <v>1</v>
       </c>
       <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
         <v>29</v>
       </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="14.5">
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="str">
         <f t="shared" si="0"/>
         <v>RPT_OPT</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="24">
         <v>1</v>
@@ -18029,102 +17882,102 @@
         <v>26</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="14.5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="24" t="str">
         <f t="shared" si="0"/>
         <v>*</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="14.5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="str">
         <f t="shared" si="0"/>
         <v>*</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="24">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="14.5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="str">
         <f t="shared" si="0"/>
         <v>*</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="24">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="14.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="24" t="str">
         <f t="shared" si="0"/>
         <v>RPT_OPT</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="24">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="14.5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="str">
         <f t="shared" si="0"/>
         <v>RPT_OPT</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="24">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H8" r:id="rId1" display="Documentation_for_the_TIMES_Model-PartIII.pdf"/>
+    <hyperlink ref="H8" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -18132,35 +17985,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B3:J26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="114.714285714286" customWidth="1"/>
-    <col min="4" max="4" width="10.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="114.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="10.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.8571428571429" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="128.25" customHeight="1">
+    <row r="3" spans="2:6" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="6" spans="2:6" ht="14.5">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="2:5" ht="15" thickBot="1">
+    <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>0</v>
       </c>
@@ -18171,38 +18024,38 @@
         <v>3</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="14.5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="14.5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="26.25" customHeight="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>4</v>
       </c>
@@ -18214,10 +18067,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="14.5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -18226,7 +18079,7 @@
         <v>C:\kristoffer\DemoS_012_timesreport\SuppXLS\[Scen_Z_TIMESReport.xlsx]RunTIMESReportScript</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="14.5">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>6</v>
       </c>
@@ -18235,7 +18088,7 @@
         <v>C:\kristoffer\DemoS_012_timesreport\SuppXLS\</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14.5">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>7</v>
       </c>
@@ -18244,9 +18097,9 @@
         <v>gams C:\kristoffer\DemoS_012_timesreport\SuppXLS\..\TIMESreport\timesreport.gms  --TIMESscenario=%$case_name%  --pathTIMESmodel=C:\kristoffer\DemoS_012_timesreport\SuppXLS\..\ --GAMS_WrkTIMES_Model=%$pathGAMS_WrkTIMES_Model%</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="14.5">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -18254,16 +18107,16 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I21" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J21" s="36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="14.5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -18274,9 +18127,9 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="2:10" ht="14.5">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="29"/>
@@ -18287,18 +18140,18 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="2:10" ht="15" thickBot="1">
+    <row r="24" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="D24" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="E24" s="31" t="s">
         <v>54</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>55</v>
       </c>
       <c r="F24" s="31" t="s">
         <v>0</v>
@@ -18310,17 +18163,17 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="2:10" ht="14.5">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="32" t="s">
         <v>56</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>57</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" s="34">
         <v>0</v>
@@ -18329,7 +18182,7 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" spans="2:10" ht="14.5">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -18345,10 +18198,10 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J21" r:id="rId1" display="VEDA: Issues when synchronizing scenario file"/>
+    <hyperlink ref="J21" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
